--- a/packages/calculators/src/modules/test/6.2-pasture-residues.xlsx
+++ b/packages/calculators/src/modules/test/6.2-pasture-residues.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10215"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11018"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/eddiesholl/Code/aginnovationaustralia/emissions-calculators/packages/calculators/src/modules/test/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/mackcheesman/Desktop/Work/EAP/Code/emissions-calculators/packages/calculators/src/modules/test/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{398C21B5-10B6-8643-B77F-A425D70507BD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C4C285A5-52F6-CE45-A817-500075BA5C3D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="51200" yWindow="12220" windowWidth="28800" windowHeight="23520" xr2:uid="{5678E890-3691-CF46-80E7-00FB1F103661}"/>
+    <workbookView xWindow="0" yWindow="620" windowWidth="28800" windowHeight="15940" xr2:uid="{5678E890-3691-CF46-80E7-00FB1F103661}"/>
   </bookViews>
   <sheets>
     <sheet name="6.2.1.1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="58" uniqueCount="34">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="59" uniqueCount="35">
   <si>
     <t>Method 1</t>
   </si>
@@ -68,9 +68,6 @@
     <t>Climate zone</t>
   </si>
   <si>
-    <t>Average yield per hectare in kg</t>
-  </si>
-  <si>
     <t>Custom values</t>
   </si>
   <si>
@@ -291,9 +288,6 @@
     <t>Ap</t>
   </si>
   <si>
-    <t>Area of pasture</t>
-  </si>
-  <si>
     <t>Yp</t>
   </si>
   <si>
@@ -340,6 +334,15 @@
   </si>
   <si>
     <t>Method 2</t>
+  </si>
+  <si>
+    <t>Average yield per hectare in t</t>
+  </si>
+  <si>
+    <t>Area of pasture in hectares</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NOTE: Pending feedback, I think this formula is incorrect. Multiplying by 10^-3 converts the yield in tonnes to gigagrams, not kilograms. I've implemented the </t>
   </si>
 </sst>
 </file>
@@ -427,7 +430,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -445,7 +448,6 @@
     <xf numFmtId="164" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="165" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -802,29 +804,31 @@
         <v>0</v>
       </c>
       <c r="L1" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="2" spans="1:16">
-      <c r="J2" s="1"/>
+      <c r="J2" s="1" t="s">
+        <v>34</v>
+      </c>
       <c r="L2" s="1"/>
     </row>
     <row r="3" spans="1:16" ht="34">
       <c r="C3" t="s">
-        <v>17</v>
+        <v>33</v>
       </c>
       <c r="D3" t="s">
-        <v>10</v>
+        <v>32</v>
       </c>
       <c r="E3" s="7" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="F3" s="7"/>
       <c r="G3" s="7"/>
       <c r="H3" s="7"/>
       <c r="I3" s="7"/>
       <c r="J3" s="1" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="L3" s="1"/>
     </row>
@@ -833,34 +837,34 @@
         <v>9</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="C4" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="D4" t="s">
         <v>16</v>
       </c>
-      <c r="D4" s="13" t="s">
-        <v>18</v>
-      </c>
       <c r="E4" t="s">
-        <v>19</v>
-      </c>
-      <c r="F4" s="13" t="s">
+        <v>17</v>
+      </c>
+      <c r="F4" t="s">
+        <v>21</v>
+      </c>
+      <c r="G4" t="s">
         <v>23</v>
       </c>
-      <c r="G4" s="13" t="s">
-        <v>25</v>
-      </c>
-      <c r="H4" s="13" t="s">
-        <v>26</v>
+      <c r="H4" t="s">
+        <v>24</v>
       </c>
       <c r="J4" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="K4" t="s">
         <v>3</v>
       </c>
       <c r="L4" s="5" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="N4" s="6" t="s">
         <v>1</v>
@@ -871,35 +875,35 @@
         <v>7</v>
       </c>
       <c r="B5" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="C5">
         <v>5000</v>
       </c>
       <c r="D5">
-        <f>IF(ISBLANK(A5), "", VLOOKUP(B5, $N$20:$S$24,2, FALSE))</f>
-        <v>4.41</v>
+        <f t="shared" ref="D5:D10" si="0">IF(ISBLANK(A5), "", VLOOKUP(B5, $N$20:$S$24,2, FALSE)/ 1000)</f>
+        <v>4.4099999999999999E-3</v>
       </c>
       <c r="E5" s="12">
-        <f>IF(ISBLANK(A5), "", VLOOKUP(B5, $N$20:$S$24,6, FALSE))</f>
+        <f t="shared" ref="E5:E10" si="1">IF(ISBLANK(A5), "", VLOOKUP(B5, $N$20:$S$24,6, FALSE))</f>
         <v>0.8</v>
       </c>
       <c r="F5" s="12">
-        <f>IF(ISBLANK(A5), "", VLOOKUP(B5, $N$20:$S$24,4, FALSE))</f>
+        <f t="shared" ref="F5:F10" si="2">IF(ISBLANK(A5), "", VLOOKUP(B5, $N$20:$S$24,4, FALSE))</f>
         <v>1.4999999999999999E-2</v>
       </c>
       <c r="G5" s="12">
-        <f>IF(ISBLANK(A5), "", VLOOKUP(B5, $N$20:$S$24,3, FALSE))</f>
+        <f t="shared" ref="G5:G10" si="3">IF(ISBLANK(A5), "", VLOOKUP(B5, $N$20:$S$24,3, FALSE))</f>
         <v>0.4</v>
       </c>
       <c r="H5" s="12">
-        <f>IF(ISBLANK(A5), "", VLOOKUP(B5, $N$20:$S$24,5, FALSE))</f>
+        <f t="shared" ref="H5:H10" si="4">IF(ISBLANK(A5), "", VLOOKUP(B5, $N$20:$S$24,5, FALSE))</f>
         <v>1.2E-2</v>
       </c>
       <c r="I5" s="12"/>
       <c r="J5">
-        <f>IF(ISBLANK(A5),"", (C5*(D5/1000) *(1 - E5)*F5)+(C5*(D5/1000)*G5*H5))</f>
-        <v>0.17198999999999998</v>
+        <f>IF(ISBLANK(A5),"", (C5*(D5 * 1000) *(1 - E5)*F5)+(C5*(D5 *1000)*G5*H5))</f>
+        <v>171.98999999999998</v>
       </c>
       <c r="K5">
         <f>IF(ISBLANK(A5),"",VLOOKUP(A5,$N$14:$O$15,2,FALSE))</f>
@@ -907,7 +911,7 @@
       </c>
       <c r="L5">
         <f>IF(ISBLANK(A5), "", J5*K5*$O$10/1000)</f>
-        <v>1.6216199999999998E-6</v>
+        <v>1.6216199999999998E-3</v>
       </c>
     </row>
     <row r="6" spans="1:16">
@@ -915,43 +919,43 @@
         <v>8</v>
       </c>
       <c r="B6" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="C6">
         <v>50</v>
       </c>
       <c r="D6">
-        <f>IF(ISBLANK(A6), "", VLOOKUP(B6, $N$20:$S$24,2, FALSE))</f>
-        <v>4.41</v>
+        <f t="shared" si="0"/>
+        <v>4.4099999999999999E-3</v>
       </c>
       <c r="E6" s="12">
-        <f>IF(ISBLANK(A6), "", VLOOKUP(B6, $N$20:$S$24,6, FALSE))</f>
+        <f t="shared" si="1"/>
         <v>0.8</v>
       </c>
       <c r="F6" s="12">
-        <f>IF(ISBLANK(A6), "", VLOOKUP(B6, $N$20:$S$24,4, FALSE))</f>
+        <f t="shared" si="2"/>
         <v>1.4999999999999999E-2</v>
       </c>
       <c r="G6" s="12">
-        <f>IF(ISBLANK(A6), "", VLOOKUP(B6, $N$20:$S$24,3, FALSE))</f>
+        <f t="shared" si="3"/>
         <v>0.4</v>
       </c>
       <c r="H6" s="12">
-        <f>IF(ISBLANK(A6), "", VLOOKUP(B6, $N$20:$S$24,5, FALSE))</f>
+        <f t="shared" si="4"/>
         <v>1.2E-2</v>
       </c>
       <c r="I6" s="12"/>
       <c r="J6">
-        <f>IF(ISBLANK(A6),"", (C6*(D6/1000) *(1 - E6)*F6)+(C6*(D6/1000)*G6*H6))</f>
-        <v>1.7198999999999999E-3</v>
+        <f t="shared" ref="J6:J20" si="5">IF(ISBLANK(A6),"", (C6*(D6 * 1000) *(1 - E6)*F6)+(C6*(D6 *1000)*G6*H6))</f>
+        <v>1.7198999999999998</v>
       </c>
       <c r="K6">
-        <f t="shared" ref="K6:K14" si="0">IF(ISBLANK(A6),"",VLOOKUP(A6,$N$14:$O$15,2,FALSE))</f>
+        <f t="shared" ref="K6" si="6">IF(ISBLANK(A6),"",VLOOKUP(A6,$N$14:$O$15,2,FALSE))</f>
         <v>5.0000000000000001E-3</v>
       </c>
       <c r="L6">
-        <f>IF(ISBLANK(A6), "", J6*K6*$O$10/1000)</f>
-        <v>1.3513499999999999E-8</v>
+        <f t="shared" ref="L6:L10" si="7">IF(ISBLANK(A6), "", J6*K6*$O$10/1000)</f>
+        <v>1.35135E-5</v>
       </c>
     </row>
     <row r="7" spans="1:16">
@@ -959,43 +963,43 @@
         <v>7</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="C7">
         <v>600</v>
       </c>
       <c r="D7">
-        <f>IF(ISBLANK(A7), "", VLOOKUP(B7, $N$20:$S$24,2, FALSE))</f>
-        <v>8.34</v>
+        <f t="shared" si="0"/>
+        <v>8.3400000000000002E-3</v>
       </c>
       <c r="E7" s="12">
-        <f>IF(ISBLANK(A7), "", VLOOKUP(B7, $N$20:$S$24,6, FALSE))</f>
+        <f t="shared" si="1"/>
         <v>0.8</v>
       </c>
       <c r="F7" s="12">
-        <f>IF(ISBLANK(A7), "", VLOOKUP(B7, $N$20:$S$24,4, FALSE))</f>
+        <f t="shared" si="2"/>
         <v>2.5000000000000001E-2</v>
       </c>
       <c r="G7" s="12">
-        <f>IF(ISBLANK(A7), "", VLOOKUP(B7, $N$20:$S$24,3, FALSE))</f>
+        <f t="shared" si="3"/>
         <v>0.8</v>
       </c>
       <c r="H7" s="12">
-        <f>IF(ISBLANK(A7), "", VLOOKUP(B7, $N$20:$S$24,5, FALSE))</f>
+        <f t="shared" si="4"/>
         <v>1.6E-2</v>
       </c>
       <c r="I7" s="12"/>
       <c r="J7">
-        <f>IF(ISBLANK(A7),"", (C7*(D7/1000) *(1 - E7)*F7)+(C7*(D7/1000)*G7*H7))</f>
-        <v>8.9071200000000017E-2</v>
+        <f t="shared" si="5"/>
+        <v>89.071200000000005</v>
       </c>
       <c r="K7">
         <f>IF(ISBLANK(A7),"",VLOOKUP(A7,$N$14:$O$15,2,FALSE))</f>
         <v>6.0000000000000001E-3</v>
       </c>
       <c r="L7">
-        <f>IF(ISBLANK(A7), "", J7*K7*$O$10/1000)</f>
-        <v>8.3981417142857172E-7</v>
+        <f t="shared" si="7"/>
+        <v>8.3981417142857135E-4</v>
       </c>
     </row>
     <row r="8" spans="1:16">
@@ -1003,43 +1007,43 @@
         <v>8</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="C8">
         <v>7000</v>
       </c>
       <c r="D8">
-        <f>IF(ISBLANK(A8), "", VLOOKUP(B8, $N$20:$S$24,2, FALSE))</f>
-        <v>8.6199999999999992</v>
+        <f t="shared" si="0"/>
+        <v>8.6199999999999992E-3</v>
       </c>
       <c r="E8" s="12">
-        <f>IF(ISBLANK(A8), "", VLOOKUP(B8, $N$20:$S$24,6, FALSE))</f>
+        <f t="shared" si="1"/>
         <v>0.8</v>
       </c>
       <c r="F8" s="12">
-        <f>IF(ISBLANK(A8), "", VLOOKUP(B8, $N$20:$S$24,4, FALSE))</f>
+        <f t="shared" si="2"/>
         <v>2.7E-2</v>
       </c>
       <c r="G8" s="12">
-        <f>IF(ISBLANK(A8), "", VLOOKUP(B8, $N$20:$S$24,3, FALSE))</f>
+        <f t="shared" si="3"/>
         <v>0.4</v>
       </c>
       <c r="H8" s="12">
-        <f>IF(ISBLANK(A8), "", VLOOKUP(B8, $N$20:$S$24,5, FALSE))</f>
+        <f t="shared" si="4"/>
         <v>1.9E-2</v>
       </c>
       <c r="I8" s="12"/>
       <c r="J8">
-        <f>IF(ISBLANK(A8),"", (C8*(D8/1000) *(1 - E8)*F8)+(C8*(D8/1000)*G8*H8))</f>
-        <v>0.7844199999999999</v>
+        <f t="shared" si="5"/>
+        <v>784.41999999999985</v>
       </c>
       <c r="K8">
         <f>IF(ISBLANK(A8),"",VLOOKUP(A8,$N$14:$O$15,2,FALSE))</f>
         <v>5.0000000000000001E-3</v>
       </c>
       <c r="L8">
-        <f>IF(ISBLANK(A8), "", J8*K8*$O$10/1000)</f>
-        <v>6.1632999999999991E-6</v>
+        <f t="shared" si="7"/>
+        <v>6.1632999999999983E-3</v>
       </c>
       <c r="N8" s="2"/>
       <c r="O8" s="2"/>
@@ -1049,43 +1053,43 @@
         <v>7</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="C9">
         <v>50</v>
       </c>
       <c r="D9">
-        <f>IF(ISBLANK(A9), "", VLOOKUP(B9, $N$20:$S$24,2, FALSE))</f>
-        <v>5.62</v>
+        <f t="shared" si="0"/>
+        <v>5.62E-3</v>
       </c>
       <c r="E9" s="12">
-        <f>IF(ISBLANK(A9), "", VLOOKUP(B9, $N$20:$S$24,6, FALSE))</f>
+        <f t="shared" si="1"/>
         <v>0.8</v>
       </c>
       <c r="F9" s="12">
-        <f>IF(ISBLANK(A9), "", VLOOKUP(B9, $N$20:$S$24,4, FALSE))</f>
+        <f t="shared" si="2"/>
         <v>2.7E-2</v>
       </c>
       <c r="G9" s="12">
-        <f>IF(ISBLANK(A9), "", VLOOKUP(B9, $N$20:$S$24,3, FALSE))</f>
+        <f t="shared" si="3"/>
         <v>0.4</v>
       </c>
       <c r="H9" s="12">
-        <f>IF(ISBLANK(A9), "", VLOOKUP(B9, $N$20:$S$24,5, FALSE))</f>
+        <f t="shared" si="4"/>
         <v>2.1999999999999999E-2</v>
       </c>
       <c r="I9" s="12"/>
       <c r="J9">
-        <f>IF(ISBLANK(A9),"", (C9*(D9/1000) *(1 - E9)*F9)+(C9*(D9/1000)*G9*H9))</f>
-        <v>3.9902000000000002E-3</v>
+        <f t="shared" si="5"/>
+        <v>3.9901999999999997</v>
       </c>
       <c r="K9">
         <f>IF(ISBLANK(A9),"",VLOOKUP(A9,$N$14:$O$15,2,FALSE))</f>
         <v>6.0000000000000001E-3</v>
       </c>
       <c r="L9">
-        <f>IF(ISBLANK(A9), "", J9*K9*$O$10/1000)</f>
-        <v>3.762188571428571E-8</v>
+        <f t="shared" si="7"/>
+        <v>3.7621885714285712E-5</v>
       </c>
       <c r="N9" s="2"/>
       <c r="O9" s="2"/>
@@ -1095,43 +1099,43 @@
         <v>8</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="C10">
         <v>50</v>
       </c>
       <c r="D10">
-        <f>IF(ISBLANK(A10), "", VLOOKUP(B10, $N$20:$S$24,2, FALSE))</f>
-        <v>8.35</v>
+        <f t="shared" si="0"/>
+        <v>8.3499999999999998E-3</v>
       </c>
       <c r="E10" s="12">
-        <f>IF(ISBLANK(A10), "", VLOOKUP(B10, $N$20:$S$24,6, FALSE))</f>
+        <f t="shared" si="1"/>
         <v>0.8</v>
       </c>
       <c r="F10" s="12">
-        <f>IF(ISBLANK(A10), "", VLOOKUP(B10, $N$20:$S$24,4, FALSE))</f>
+        <f t="shared" si="2"/>
         <v>1.4999999999999999E-2</v>
       </c>
       <c r="G10" s="12">
-        <f>IF(ISBLANK(A10), "", VLOOKUP(B10, $N$20:$S$24,3, FALSE))</f>
+        <f t="shared" si="3"/>
         <v>0.8</v>
       </c>
       <c r="H10" s="12">
-        <f>IF(ISBLANK(A10), "", VLOOKUP(B10, $N$20:$S$24,5, FALSE))</f>
+        <f t="shared" si="4"/>
         <v>1.2E-2</v>
       </c>
       <c r="I10" s="12"/>
       <c r="J10">
-        <f>IF(ISBLANK(A10),"", (C10*(D10/1000) *(1 - E10)*F10)+(C10*(D10/1000)*G10*H10))</f>
-        <v>5.2604999999999996E-3</v>
+        <f t="shared" si="5"/>
+        <v>5.2604999999999995</v>
       </c>
       <c r="K10">
         <f>IF(ISBLANK(A10),"",VLOOKUP(A10,$N$14:$O$15,2,FALSE))</f>
         <v>5.0000000000000001E-3</v>
       </c>
       <c r="L10">
-        <f>IF(ISBLANK(A10), "", J10*K10*$O$10/1000)</f>
-        <v>4.1332499999999996E-8</v>
+        <f t="shared" si="7"/>
+        <v>4.1332500000000004E-5</v>
       </c>
       <c r="N10" t="s">
         <v>2</v>
@@ -1143,32 +1147,32 @@
     </row>
     <row r="11" spans="1:16">
       <c r="E11" s="12" t="str">
-        <f t="shared" ref="E11:E20" si="1">IF(ISBLANK(A11), "", VLOOKUP(B11, $N$20:$S$24,6, FALSE))</f>
+        <f t="shared" ref="E11:E20" si="8">IF(ISBLANK(A11), "", VLOOKUP(B11, $N$20:$S$24,6, FALSE))</f>
         <v/>
       </c>
       <c r="F11" s="12" t="str">
-        <f t="shared" ref="F11:F20" si="2">IF(ISBLANK(A11), "", VLOOKUP(B11, $N$20:$S$24,4, FALSE))</f>
+        <f t="shared" ref="F11:F20" si="9">IF(ISBLANK(A11), "", VLOOKUP(B11, $N$20:$S$24,4, FALSE))</f>
         <v/>
       </c>
       <c r="G11" s="12" t="str">
-        <f t="shared" ref="G11:G20" si="3">IF(ISBLANK(A11), "", VLOOKUP(B11, $N$20:$S$24,3, FALSE))</f>
+        <f t="shared" ref="G11:G20" si="10">IF(ISBLANK(A11), "", VLOOKUP(B11, $N$20:$S$24,3, FALSE))</f>
         <v/>
       </c>
       <c r="H11" s="12" t="str">
-        <f t="shared" ref="H11:H20" si="4">IF(ISBLANK(A11), "", VLOOKUP(B11, $N$20:$S$24,5, FALSE))</f>
+        <f t="shared" ref="H11:H20" si="11">IF(ISBLANK(A11), "", VLOOKUP(B11, $N$20:$S$24,5, FALSE))</f>
         <v/>
       </c>
       <c r="I11" s="12"/>
       <c r="J11" t="str">
-        <f t="shared" ref="J11:J20" si="5">IF(ISBLANK(A11),"", (C11*(D11/1000) *(1 - E11)*F11)+(C11*(D11/1000)*G11*H11))</f>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K11" t="str">
-        <f t="shared" ref="K11:K20" si="6">IF(ISBLANK(A11),"",VLOOKUP(A11,$N$14:$O$15,2,FALSE))</f>
+        <f t="shared" ref="K11:K20" si="12">IF(ISBLANK(A11),"",VLOOKUP(A11,$N$14:$O$15,2,FALSE))</f>
         <v/>
       </c>
       <c r="L11" t="str">
-        <f t="shared" ref="L11:L20" si="7">IF(ISBLANK(A11), "", J11*K11*$O$10/1000)</f>
+        <f t="shared" ref="L11:L20" si="13">IF(ISBLANK(A11), "", J11*K11*$O$10/1000)</f>
         <v/>
       </c>
       <c r="N11" s="2"/>
@@ -1181,19 +1185,19 @@
         <v/>
       </c>
       <c r="E12" s="12" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="F12" s="12" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="G12" s="12" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="H12" s="12" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="I12" s="12"/>
@@ -1202,11 +1206,11 @@
         <v/>
       </c>
       <c r="K12" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="L12" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="N12" s="2" t="s">
@@ -1221,19 +1225,19 @@
         <v/>
       </c>
       <c r="E13" s="12" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="F13" s="12" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="G13" s="12" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="H13" s="12" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="I13" s="12"/>
@@ -1242,11 +1246,11 @@
         <v/>
       </c>
       <c r="K13" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="L13" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="N13" t="s">
@@ -1260,19 +1264,19 @@
         <v/>
       </c>
       <c r="E14" s="12" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="F14" s="12" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="G14" s="12" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="H14" s="12" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="I14" s="12"/>
@@ -1281,11 +1285,11 @@
         <v/>
       </c>
       <c r="K14" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="L14" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="N14" s="2" t="s">
@@ -1300,22 +1304,22 @@
     </row>
     <row r="15" spans="1:16">
       <c r="B15" s="2" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="E15" s="12" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="F15" s="12" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="G15" s="12" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="H15" s="12" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="I15" s="12"/>
@@ -1324,11 +1328,11 @@
         <v/>
       </c>
       <c r="K15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="L15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="N15" s="2" t="s">
@@ -1344,22 +1348,22 @@
     <row r="16" spans="1:16">
       <c r="B16" s="2"/>
       <c r="D16" s="4" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="E16" s="12" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="F16" s="12" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="G16" s="12" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="H16" s="12" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="I16" s="12"/>
@@ -1368,11 +1372,11 @@
         <v/>
       </c>
       <c r="K16" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="L16" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="N16" s="2"/>
@@ -1384,7 +1388,7 @@
         <v>8</v>
       </c>
       <c r="B17" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="C17">
         <v>50</v>
@@ -1393,33 +1397,33 @@
         <v>0.5</v>
       </c>
       <c r="E17" s="12">
-        <f t="shared" si="1"/>
+        <f t="shared" si="8"/>
         <v>0.8</v>
       </c>
       <c r="F17" s="12">
-        <f t="shared" si="2"/>
+        <f t="shared" si="9"/>
         <v>1.4999999999999999E-2</v>
       </c>
       <c r="G17" s="12">
-        <f t="shared" si="3"/>
+        <f t="shared" si="10"/>
         <v>0.4</v>
       </c>
       <c r="H17" s="12">
-        <f t="shared" si="4"/>
+        <f t="shared" si="11"/>
         <v>1.2E-2</v>
       </c>
       <c r="I17" s="12"/>
       <c r="J17">
         <f t="shared" si="5"/>
-        <v>1.9500000000000002E-4</v>
+        <v>195</v>
       </c>
       <c r="K17">
-        <f t="shared" si="6"/>
+        <f t="shared" si="12"/>
         <v>5.0000000000000001E-3</v>
       </c>
       <c r="L17">
-        <f t="shared" si="7"/>
-        <v>1.5321428571428575E-9</v>
+        <f t="shared" si="13"/>
+        <v>1.5321428571428571E-3</v>
       </c>
     </row>
     <row r="18" spans="1:22">
@@ -1427,7 +1431,7 @@
         <v>7</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="C18">
         <v>600</v>
@@ -1436,33 +1440,33 @@
         <v>1</v>
       </c>
       <c r="E18" s="12">
-        <f t="shared" si="1"/>
+        <f t="shared" si="8"/>
         <v>0.8</v>
       </c>
       <c r="F18" s="12">
-        <f t="shared" si="2"/>
+        <f t="shared" si="9"/>
         <v>2.5000000000000001E-2</v>
       </c>
       <c r="G18" s="12">
-        <f t="shared" si="3"/>
+        <f t="shared" si="10"/>
         <v>0.8</v>
       </c>
       <c r="H18" s="12">
-        <f t="shared" si="4"/>
+        <f t="shared" si="11"/>
         <v>1.6E-2</v>
       </c>
       <c r="I18" s="12"/>
       <c r="J18">
         <f t="shared" si="5"/>
-        <v>1.0679999999999999E-2</v>
+        <v>10680</v>
       </c>
       <c r="K18">
-        <f t="shared" si="6"/>
+        <f t="shared" si="12"/>
         <v>6.0000000000000001E-3</v>
       </c>
       <c r="L18">
-        <f t="shared" si="7"/>
-        <v>1.0069714285714285E-7</v>
+        <f t="shared" si="13"/>
+        <v>0.10069714285714285</v>
       </c>
       <c r="N18" s="2"/>
       <c r="O18" s="2"/>
@@ -1472,7 +1476,7 @@
         <v>8</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="C19">
         <v>7000</v>
@@ -1481,51 +1485,51 @@
         <v>10</v>
       </c>
       <c r="E19" s="12">
-        <f t="shared" si="1"/>
+        <f t="shared" si="8"/>
         <v>0.8</v>
       </c>
       <c r="F19" s="12">
-        <f t="shared" si="2"/>
+        <f t="shared" si="9"/>
         <v>2.7E-2</v>
       </c>
       <c r="G19" s="12">
-        <f t="shared" si="3"/>
+        <f t="shared" si="10"/>
         <v>0.4</v>
       </c>
       <c r="H19" s="12">
-        <f t="shared" si="4"/>
+        <f t="shared" si="11"/>
         <v>1.9E-2</v>
       </c>
       <c r="I19" s="12"/>
       <c r="J19">
         <f t="shared" si="5"/>
-        <v>0.90999999999999992</v>
+        <v>909999.99999999988</v>
       </c>
       <c r="K19">
-        <f t="shared" si="6"/>
+        <f t="shared" si="12"/>
         <v>5.0000000000000001E-3</v>
       </c>
       <c r="L19">
-        <f t="shared" si="7"/>
-        <v>7.1499999999999993E-6</v>
+        <f t="shared" si="13"/>
+        <v>7.1499999999999986</v>
       </c>
       <c r="N19" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="O19" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="P19" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="Q19" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="O19" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="P19" s="2" t="s">
+      <c r="R19" s="7" t="s">
         <v>22</v>
       </c>
-      <c r="Q19" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="R19" s="7" t="s">
-        <v>24</v>
-      </c>
       <c r="S19" s="2" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
     </row>
     <row r="20" spans="1:22">
@@ -1533,7 +1537,7 @@
         <v>7</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="C20">
         <v>50</v>
@@ -1542,36 +1546,36 @@
         <v>12.5</v>
       </c>
       <c r="E20" s="12">
-        <f t="shared" si="1"/>
+        <f t="shared" si="8"/>
         <v>0.8</v>
       </c>
       <c r="F20" s="12">
-        <f t="shared" si="2"/>
+        <f t="shared" si="9"/>
         <v>2.7E-2</v>
       </c>
       <c r="G20" s="12">
-        <f t="shared" si="3"/>
+        <f t="shared" si="10"/>
         <v>0.4</v>
       </c>
       <c r="H20" s="12">
-        <f t="shared" si="4"/>
+        <f t="shared" si="11"/>
         <v>2.1999999999999999E-2</v>
       </c>
       <c r="I20" s="12"/>
       <c r="J20">
         <f t="shared" si="5"/>
-        <v>8.8749999999999992E-3</v>
+        <v>8875</v>
       </c>
       <c r="K20">
-        <f t="shared" si="6"/>
+        <f t="shared" si="12"/>
         <v>6.0000000000000001E-3</v>
       </c>
       <c r="L20">
-        <f t="shared" si="7"/>
-        <v>8.3678571428571417E-8</v>
+        <f t="shared" si="13"/>
+        <v>8.3678571428571435E-2</v>
       </c>
       <c r="N20" s="2" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="O20" s="2">
         <v>4.41</v>
@@ -1591,7 +1595,7 @@
     </row>
     <row r="21" spans="1:22">
       <c r="N21" s="2" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="O21" s="2">
         <v>8.34</v>
@@ -1611,7 +1615,7 @@
     </row>
     <row r="22" spans="1:22">
       <c r="N22" s="2" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="O22" s="2">
         <v>8.6199999999999992</v>
@@ -1635,7 +1639,7 @@
     <row r="23" spans="1:22">
       <c r="B23" s="2"/>
       <c r="N23" s="2" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="O23" s="2">
         <v>5.62</v>
@@ -1659,7 +1663,7 @@
     <row r="24" spans="1:22">
       <c r="B24" s="2"/>
       <c r="N24" s="2" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="O24" s="2">
         <v>8.35</v>

--- a/packages/calculators/src/modules/test/6.2-pasture-residues.xlsx
+++ b/packages/calculators/src/modules/test/6.2-pasture-residues.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/mackcheesman/Desktop/Work/EAP/Code/emissions-calculators/packages/calculators/src/modules/test/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C4C285A5-52F6-CE45-A817-500075BA5C3D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BFB2E7BA-DCAD-274A-9855-2AB25038F3AF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="620" windowWidth="28800" windowHeight="15940" xr2:uid="{5678E890-3691-CF46-80E7-00FB1F103661}"/>
+    <workbookView xWindow="-20" yWindow="620" windowWidth="28800" windowHeight="15900" xr2:uid="{5678E890-3691-CF46-80E7-00FB1F103661}"/>
   </bookViews>
   <sheets>
     <sheet name="6.2.1.1" sheetId="1" r:id="rId1"/>
@@ -166,6 +166,69 @@
     </r>
   </si>
   <si>
+    <t>En2o</t>
+  </si>
+  <si>
+    <t>Mp</t>
+  </si>
+  <si>
+    <t>Ap</t>
+  </si>
+  <si>
+    <t>Yp</t>
+  </si>
+  <si>
+    <t>FFODp</t>
+  </si>
+  <si>
+    <t>Fraction of pasture removed</t>
+  </si>
+  <si>
+    <t>Table A.2.1.3</t>
+  </si>
+  <si>
+    <t>Rbgp</t>
+  </si>
+  <si>
+    <t>Ncagp</t>
+  </si>
+  <si>
+    <t>NCbgp</t>
+  </si>
+  <si>
+    <t>RBGp</t>
+  </si>
+  <si>
+    <t>NCBGp</t>
+  </si>
+  <si>
+    <t>Pasture type</t>
+  </si>
+  <si>
+    <t>Annual grass</t>
+  </si>
+  <si>
+    <t>Grass clover mixture</t>
+  </si>
+  <si>
+    <t>Lucerne</t>
+  </si>
+  <si>
+    <t>Other legume</t>
+  </si>
+  <si>
+    <t>Perennial pasture</t>
+  </si>
+  <si>
+    <t>Method 2</t>
+  </si>
+  <si>
+    <t>Average yield per hectare in t</t>
+  </si>
+  <si>
+    <t>Area of pasture in hectares</t>
+  </si>
+  <si>
     <r>
       <t>𝑀</t>
     </r>
@@ -221,7 +284,7 @@
         <rFont val="Helvetica"/>
         <family val="2"/>
       </rPr>
-      <t>× 10</t>
+      <t>× 10^</t>
     </r>
     <r>
       <rPr>
@@ -230,7 +293,7 @@
         <rFont val="Helvetica"/>
         <family val="2"/>
       </rPr>
-      <t>−3</t>
+      <t>3</t>
     </r>
     <r>
       <rPr>
@@ -275,74 +338,11 @@
         <rFont val="Helvetica"/>
         <family val="2"/>
       </rPr>
-      <t>) + (𝐴𝑝 × (𝑌 𝑝 × 10−3) × 𝑅𝐵𝐺𝑝 × 𝑁𝐶𝐵𝐺𝑝)</t>
-    </r>
-  </si>
-  <si>
-    <t>En2o</t>
-  </si>
-  <si>
-    <t>Mp</t>
-  </si>
-  <si>
-    <t>Ap</t>
-  </si>
-  <si>
-    <t>Yp</t>
-  </si>
-  <si>
-    <t>FFODp</t>
-  </si>
-  <si>
-    <t>Fraction of pasture removed</t>
-  </si>
-  <si>
-    <t>Table A.2.1.3</t>
-  </si>
-  <si>
-    <t>Rbgp</t>
-  </si>
-  <si>
-    <t>Ncagp</t>
-  </si>
-  <si>
-    <t>NCbgp</t>
-  </si>
-  <si>
-    <t>RBGp</t>
-  </si>
-  <si>
-    <t>NCBGp</t>
-  </si>
-  <si>
-    <t>Pasture type</t>
-  </si>
-  <si>
-    <t>Annual grass</t>
-  </si>
-  <si>
-    <t>Grass clover mixture</t>
-  </si>
-  <si>
-    <t>Lucerne</t>
-  </si>
-  <si>
-    <t>Other legume</t>
-  </si>
-  <si>
-    <t>Perennial pasture</t>
-  </si>
-  <si>
-    <t>Method 2</t>
-  </si>
-  <si>
-    <t>Average yield per hectare in t</t>
-  </si>
-  <si>
-    <t>Area of pasture in hectares</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NOTE: Pending feedback, I think this formula is incorrect. Multiplying by 10^-3 converts the yield in tonnes to gigagrams, not kilograms. I've implemented the </t>
+      <t>) + (𝐴𝑝 × (𝑌 𝑝 × 10^3) × 𝑅𝐵𝐺𝑝 × 𝑁𝐶𝐵𝐺𝑝)</t>
+    </r>
+  </si>
+  <si>
+    <t>NOTE: Pending feedback, I think this formula is incorrect. Multiplying by 10^-3 converts the yield in tonnes to gigagrams, not kilograms. I've implemented this with what I think is the correct conversion</t>
   </si>
 </sst>
 </file>
@@ -815,20 +815,20 @@
     </row>
     <row r="3" spans="1:16" ht="34">
       <c r="C3" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="D3" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="E3" s="7" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="F3" s="7"/>
       <c r="G3" s="7"/>
       <c r="H3" s="7"/>
       <c r="I3" s="7"/>
       <c r="J3" s="1" t="s">
-        <v>12</v>
+        <v>33</v>
       </c>
       <c r="L3" s="1"/>
     </row>
@@ -837,34 +837,34 @@
         <v>9</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C4" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="D4" t="s">
         <v>15</v>
       </c>
-      <c r="D4" t="s">
+      <c r="E4" t="s">
         <v>16</v>
       </c>
-      <c r="E4" t="s">
-        <v>17</v>
-      </c>
       <c r="F4" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="G4" t="s">
+        <v>22</v>
+      </c>
+      <c r="H4" t="s">
         <v>23</v>
       </c>
-      <c r="H4" t="s">
-        <v>24</v>
-      </c>
       <c r="J4" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="K4" t="s">
         <v>3</v>
       </c>
       <c r="L4" s="5" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="N4" s="6" t="s">
         <v>1</v>
@@ -875,7 +875,7 @@
         <v>7</v>
       </c>
       <c r="B5" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C5">
         <v>5000</v>
@@ -919,7 +919,7 @@
         <v>8</v>
       </c>
       <c r="B6" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C6">
         <v>50</v>
@@ -963,7 +963,7 @@
         <v>7</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="C7">
         <v>600</v>
@@ -1007,7 +1007,7 @@
         <v>8</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C8">
         <v>7000</v>
@@ -1053,7 +1053,7 @@
         <v>7</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C9">
         <v>50</v>
@@ -1099,7 +1099,7 @@
         <v>8</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C10">
         <v>50</v>
@@ -1304,7 +1304,7 @@
     </row>
     <row r="15" spans="1:16">
       <c r="B15" s="2" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="E15" s="12" t="str">
         <f t="shared" si="8"/>
@@ -1388,7 +1388,7 @@
         <v>8</v>
       </c>
       <c r="B17" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C17">
         <v>50</v>
@@ -1431,7 +1431,7 @@
         <v>7</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="C18">
         <v>600</v>
@@ -1476,7 +1476,7 @@
         <v>8</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C19">
         <v>7000</v>
@@ -1514,22 +1514,22 @@
         <v>7.1499999999999986</v>
       </c>
       <c r="N19" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="O19" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="P19" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="O19" s="2" t="s">
+      <c r="Q19" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="R19" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="S19" s="2" t="s">
         <v>16</v>
-      </c>
-      <c r="P19" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="Q19" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="R19" s="7" t="s">
-        <v>22</v>
-      </c>
-      <c r="S19" s="2" t="s">
-        <v>17</v>
       </c>
     </row>
     <row r="20" spans="1:22">
@@ -1537,7 +1537,7 @@
         <v>7</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C20">
         <v>50</v>
@@ -1575,7 +1575,7 @@
         <v>8.3678571428571435E-2</v>
       </c>
       <c r="N20" s="2" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="O20" s="2">
         <v>4.41</v>
@@ -1595,7 +1595,7 @@
     </row>
     <row r="21" spans="1:22">
       <c r="N21" s="2" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="O21" s="2">
         <v>8.34</v>
@@ -1615,7 +1615,7 @@
     </row>
     <row r="22" spans="1:22">
       <c r="N22" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="O22" s="2">
         <v>8.6199999999999992</v>
@@ -1639,7 +1639,7 @@
     <row r="23" spans="1:22">
       <c r="B23" s="2"/>
       <c r="N23" s="2" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="O23" s="2">
         <v>5.62</v>
@@ -1663,7 +1663,7 @@
     <row r="24" spans="1:22">
       <c r="B24" s="2"/>
       <c r="N24" s="2" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="O24" s="2">
         <v>8.35</v>
